--- a/execution-substrates/xlsx/rulebook.xlsx
+++ b/execution-substrates/xlsx/rulebook.xlsx
@@ -442,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:AP34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -453,24 +453,40 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="12" customWidth="1" min="13" max="13"/>
-    <col width="17" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="27" customWidth="1" min="16" max="16"/>
-    <col width="22" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="29" customWidth="1" min="22" max="22"/>
-    <col width="28" customWidth="1" min="23" max="23"/>
-    <col width="23" customWidth="1" min="24" max="24"/>
-    <col width="26" customWidth="1" min="25" max="25"/>
-    <col width="12" customWidth="1" min="26" max="26"/>
+    <col width="34" customWidth="1" min="9" max="9"/>
+    <col width="36" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="17" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
+    <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="15" customWidth="1" min="22" max="22"/>
+    <col width="17" customWidth="1" min="23" max="23"/>
+    <col width="21" customWidth="1" min="24" max="24"/>
+    <col width="29" customWidth="1" min="25" max="25"/>
+    <col width="28" customWidth="1" min="26" max="26"/>
+    <col width="23" customWidth="1" min="27" max="27"/>
+    <col width="26" customWidth="1" min="28" max="28"/>
+    <col width="12" customWidth="1" min="29" max="29"/>
+    <col width="20" customWidth="1" min="30" max="30"/>
+    <col width="22" customWidth="1" min="31" max="31"/>
+    <col width="21" customWidth="1" min="32" max="32"/>
+    <col width="28" customWidth="1" min="33" max="33"/>
+    <col width="21" customWidth="1" min="34" max="34"/>
+    <col width="21" customWidth="1" min="35" max="35"/>
+    <col width="29" customWidth="1" min="36" max="36"/>
+    <col width="27" customWidth="1" min="37" max="37"/>
+    <col width="17" customWidth="1" min="38" max="38"/>
+    <col width="30" customWidth="1" min="39" max="39"/>
+    <col width="20" customWidth="1" min="40" max="40"/>
+    <col width="34" customWidth="1" min="41" max="41"/>
+    <col width="21" customWidth="1" min="42" max="42"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,92 +532,172 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>PredictedBiologicalLanguage_Core</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>PredictedBiologicalLanguage_Strict</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HockettScore</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>PredictionPredicates</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>PredictionFail</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>HasIdentity</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>IsParsed</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>ResolvesToAnAST</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>HasLinearDecodingPressure</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>IsStableOntologyReference</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>IsLiveOntologyEditor</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>IsOpenWorld</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>IsClosedWorld</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>IsDescriptionOf</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>DistanceFromConcept</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>IsOpenClosedWorldConflicted</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>DimensionalityWhileEditing</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>RelationshipToConcept</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>ModelObjectFacilityLayer</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>SortOrder</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasSemanticity</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasArbitrariness</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDiscreteness</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDualityOfPatterning</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasProductivity</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasDisplacement</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasCulturalTransmission</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasInterchangeability</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasFeedback</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasBroadcastTransmission</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_HasRapidFading</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_IsEvolvedCommunicationSystem</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>Bio_PrimaryModality</t>
         </is>
       </c>
     </row>
@@ -634,84 +730,163 @@
         <v/>
       </c>
       <c r="H2" s="3">
+        <f>OR(
+  AND(
+    $E2,
+    $P2,
+    $W2,
+    $R2,
+    $Q2,
+    $S2,
+    NOT($F2),
+    NOT($O2)
+  ),
+  $K2 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I2" s="3">
         <f>AND(
-  $E2,
-  $M2,
-  $T2,
-  $O2,
-  $N2,
-  $P2,
-  NOT($F2),
-  NOT($L2)
-)</f>
-        <v/>
-      </c>
-      <c r="I2" s="3">
-        <f>IF($E2, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M2, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T2, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O2, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N2, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P2, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F2, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L2, "Has Identity", "Has no Identity")</f>
+  $AO2,
+  $AD2,
+  $AE2,
+  $AF2,
+  $AG2,
+  $AH2,
+  $AI2,
+  $AJ2
+)</f>
         <v/>
       </c>
       <c r="J2" s="3">
+        <f>AND(
+  $I2,
+  $AK2,
+  $AL2
+)</f>
+        <v/>
+      </c>
+      <c r="K2" s="3">
+        <f>SUM(IF($AD2,1,0),
+IF($AE2,1,0),
+IF($AF2,1,0),
+IF($AG2,1,0),
+IF($AH2,1,0),
+IF($AI2,1,0),
+IF($AJ2,1,0),
+IF($AK2,1,0),
+IF($AL2,1,0),
+IF($AM2,1,0),
+IF($AN2,1,0))</f>
+        <v/>
+      </c>
+      <c r="L2" s="3">
+        <f>IF($E2, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P2, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W2, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R2, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q2, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S2, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F2, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O2, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M2" s="3">
         <f>IF(NOT($H2 = $C2),
   $B2 &amp; " " &amp; IF($H2, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C2, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V2, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
+  IF($C2, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y2, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N2" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O2" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q2" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S2" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T2" s="3">
-        <f>$U2 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W2" s="3">
+        <f>$X2 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X2" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V2" s="3">
-        <f>AND($R2, $S2)</f>
-        <v/>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="Y2" s="3">
+        <f>AND($U2, $V2)</f>
+        <v/>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X2" s="3">
-        <f>IF($U2 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AA2" s="3">
+        <f>IF($X2 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="n">
-        <v>1</v>
+      <c r="AC2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO2" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -743,44 +918,73 @@
         <v/>
       </c>
       <c r="H3" s="3">
+        <f>OR(
+  AND(
+    $E3,
+    $P3,
+    $W3,
+    $R3,
+    $Q3,
+    $S3,
+    NOT($F3),
+    NOT($O3)
+  ),
+  $K3 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I3" s="3">
         <f>AND(
-  $E3,
-  $M3,
-  $T3,
-  $O3,
-  $N3,
-  $P3,
-  NOT($F3),
-  NOT($L3)
-)</f>
-        <v/>
-      </c>
-      <c r="I3" s="3">
-        <f>IF($E3, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M3, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T3, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O3, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N3, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P3, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F3, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L3, "Has Identity", "Has no Identity")</f>
+  $AO3,
+  $AD3,
+  $AE3,
+  $AF3,
+  $AG3,
+  $AH3,
+  $AI3,
+  $AJ3
+)</f>
         <v/>
       </c>
       <c r="J3" s="3">
+        <f>AND(
+  $I3,
+  $AK3,
+  $AL3
+)</f>
+        <v/>
+      </c>
+      <c r="K3" s="3">
+        <f>SUM(IF($AD3,1,0),
+IF($AE3,1,0),
+IF($AF3,1,0),
+IF($AG3,1,0),
+IF($AH3,1,0),
+IF($AI3,1,0),
+IF($AJ3,1,0),
+IF($AK3,1,0),
+IF($AL3,1,0),
+IF($AM3,1,0),
+IF($AN3,1,0))</f>
+        <v/>
+      </c>
+      <c r="L3" s="3">
+        <f>IF($E3, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P3, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W3, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R3, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q3, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S3, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F3, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O3, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M3" s="3">
         <f>IF(NOT($H3 = $C3),
   $B3 &amp; " " &amp; IF($H3, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C3, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V3, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
+  IF($C3, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y3, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M3" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N3" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" s="2" t="b">
         <v>0</v>
@@ -792,36 +996,82 @@
         <v>0</v>
       </c>
       <c r="S3" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" s="3">
-        <f>$U3 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3">
-        <f>AND($R3, $S3)</f>
-        <v/>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3" s="3">
+        <f>$X3 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="3">
+        <f>AND($U3, $V3)</f>
+        <v/>
+      </c>
+      <c r="Z3" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X3" s="3">
-        <f>IF($U3 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y3" s="2" t="inlineStr">
+      <c r="AA3" s="3">
+        <f>IF($X3 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z3" s="2" t="n">
+      <c r="AC3" s="2" t="n">
         <v>2</v>
       </c>
+      <c r="AD3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -852,84 +1102,163 @@
         <v/>
       </c>
       <c r="H4" s="3">
+        <f>OR(
+  AND(
+    $E4,
+    $P4,
+    $W4,
+    $R4,
+    $Q4,
+    $S4,
+    NOT($F4),
+    NOT($O4)
+  ),
+  $K4 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I4" s="3">
         <f>AND(
-  $E4,
-  $M4,
-  $T4,
-  $O4,
-  $N4,
-  $P4,
-  NOT($F4),
-  NOT($L4)
-)</f>
-        <v/>
-      </c>
-      <c r="I4" s="3">
-        <f>IF($E4, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M4, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T4, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O4, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N4, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P4, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F4, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L4, "Has Identity", "Has no Identity")</f>
+  $AO4,
+  $AD4,
+  $AE4,
+  $AF4,
+  $AG4,
+  $AH4,
+  $AI4,
+  $AJ4
+)</f>
         <v/>
       </c>
       <c r="J4" s="3">
+        <f>AND(
+  $I4,
+  $AK4,
+  $AL4
+)</f>
+        <v/>
+      </c>
+      <c r="K4" s="3">
+        <f>SUM(IF($AD4,1,0),
+IF($AE4,1,0),
+IF($AF4,1,0),
+IF($AG4,1,0),
+IF($AH4,1,0),
+IF($AI4,1,0),
+IF($AJ4,1,0),
+IF($AK4,1,0),
+IF($AL4,1,0),
+IF($AM4,1,0),
+IF($AN4,1,0))</f>
+        <v/>
+      </c>
+      <c r="L4" s="3">
+        <f>IF($E4, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P4, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W4, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R4, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q4, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S4, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F4, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O4, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M4" s="3">
         <f>IF(NOT($H4 = $C4),
   $B4 &amp; " " &amp; IF($H4, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C4, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V4, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+  IF($C4, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y4, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M4" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N4" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O4" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R4" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S4" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3">
-        <f>$U4 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W4" s="3">
+        <f>$X4 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V4" s="3">
-        <f>AND($R4, $S4)</f>
-        <v/>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="Y4" s="3">
+        <f>AND($U4, $V4)</f>
+        <v/>
+      </c>
+      <c r="Z4" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X4" s="3">
-        <f>IF($U4 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y4" s="2" t="inlineStr">
+      <c r="AA4" s="3">
+        <f>IF($X4 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z4" s="2" t="n">
+      <c r="AC4" s="2" t="n">
         <v>3</v>
+      </c>
+      <c r="AD4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -961,47 +1290,76 @@
         <v/>
       </c>
       <c r="H5" s="3">
+        <f>OR(
+  AND(
+    $E5,
+    $P5,
+    $W5,
+    $R5,
+    $Q5,
+    $S5,
+    NOT($F5),
+    NOT($O5)
+  ),
+  $K5 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I5" s="3">
         <f>AND(
-  $E5,
-  $M5,
-  $T5,
-  $O5,
-  $N5,
-  $P5,
-  NOT($F5),
-  NOT($L5)
-)</f>
-        <v/>
-      </c>
-      <c r="I5" s="3">
-        <f>IF($E5, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M5, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T5, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O5, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N5, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P5, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F5, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L5, "Has Identity", "Has no Identity")</f>
+  $AO5,
+  $AD5,
+  $AE5,
+  $AF5,
+  $AG5,
+  $AH5,
+  $AI5,
+  $AJ5
+)</f>
         <v/>
       </c>
       <c r="J5" s="3">
+        <f>AND(
+  $I5,
+  $AK5,
+  $AL5
+)</f>
+        <v/>
+      </c>
+      <c r="K5" s="3">
+        <f>SUM(IF($AD5,1,0),
+IF($AE5,1,0),
+IF($AF5,1,0),
+IF($AG5,1,0),
+IF($AH5,1,0),
+IF($AI5,1,0),
+IF($AJ5,1,0),
+IF($AK5,1,0),
+IF($AL5,1,0),
+IF($AM5,1,0),
+IF($AN5,1,0))</f>
+        <v/>
+      </c>
+      <c r="L5" s="3">
+        <f>IF($E5, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P5, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W5, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R5, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q5, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S5, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F5, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O5, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M5" s="3">
         <f>IF(NOT($H5 = $C5),
   $B5 &amp; " " &amp; IF($H5, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C5, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V5, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
+  IF($C5, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y5, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N5" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P5" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" s="2" t="b">
         <v>0</v>
@@ -1010,36 +1368,82 @@
         <v>0</v>
       </c>
       <c r="S5" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T5" s="3">
-        <f>$U5 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3">
-        <f>AND($R5, $S5)</f>
-        <v/>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V5" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5" s="3">
+        <f>$X5 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="3">
+        <f>AND($U5, $V5)</f>
+        <v/>
+      </c>
+      <c r="Z5" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X5" s="3">
-        <f>IF($U5 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y5" s="2" t="inlineStr">
+      <c r="AA5" s="3">
+        <f>IF($X5 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z5" s="2" t="n">
+      <c r="AC5" s="2" t="n">
         <v>4</v>
       </c>
+      <c r="AD5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1070,84 +1474,163 @@
         <v/>
       </c>
       <c r="H6" s="3">
+        <f>OR(
+  AND(
+    $E6,
+    $P6,
+    $W6,
+    $R6,
+    $Q6,
+    $S6,
+    NOT($F6),
+    NOT($O6)
+  ),
+  $K6 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I6" s="3">
         <f>AND(
-  $E6,
-  $M6,
-  $T6,
-  $O6,
-  $N6,
-  $P6,
-  NOT($F6),
-  NOT($L6)
-)</f>
-        <v/>
-      </c>
-      <c r="I6" s="3">
-        <f>IF($E6, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M6, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T6, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O6, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N6, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P6, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F6, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L6, "Has Identity", "Has no Identity")</f>
+  $AO6,
+  $AD6,
+  $AE6,
+  $AF6,
+  $AG6,
+  $AH6,
+  $AI6,
+  $AJ6
+)</f>
         <v/>
       </c>
       <c r="J6" s="3">
+        <f>AND(
+  $I6,
+  $AK6,
+  $AL6
+)</f>
+        <v/>
+      </c>
+      <c r="K6" s="3">
+        <f>SUM(IF($AD6,1,0),
+IF($AE6,1,0),
+IF($AF6,1,0),
+IF($AG6,1,0),
+IF($AH6,1,0),
+IF($AI6,1,0),
+IF($AJ6,1,0),
+IF($AK6,1,0),
+IF($AL6,1,0),
+IF($AM6,1,0),
+IF($AN6,1,0))</f>
+        <v/>
+      </c>
+      <c r="L6" s="3">
+        <f>IF($E6, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P6, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W6, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R6, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q6, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S6, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F6, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O6, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M6" s="3">
         <f>IF(NOT($H6 = $C6),
   $B6 &amp; " " &amp; IF($H6, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C6, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V6, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+  IF($C6, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y6, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N6" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O6" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q6" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R6" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S6" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3">
-        <f>$U6 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V6" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W6" s="3">
+        <f>$X6 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V6" s="3">
-        <f>AND($R6, $S6)</f>
-        <v/>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
+      <c r="Y6" s="3">
+        <f>AND($U6, $V6)</f>
+        <v/>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X6" s="3">
-        <f>IF($U6 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y6" s="2" t="inlineStr">
+      <c r="AA6" s="3">
+        <f>IF($X6 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z6" s="2" t="n">
+      <c r="AC6" s="2" t="n">
         <v>5</v>
+      </c>
+      <c r="AD6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -1179,47 +1662,76 @@
         <v/>
       </c>
       <c r="H7" s="3">
+        <f>OR(
+  AND(
+    $E7,
+    $P7,
+    $W7,
+    $R7,
+    $Q7,
+    $S7,
+    NOT($F7),
+    NOT($O7)
+  ),
+  $K7 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I7" s="3">
         <f>AND(
-  $E7,
-  $M7,
-  $T7,
-  $O7,
-  $N7,
-  $P7,
-  NOT($F7),
-  NOT($L7)
-)</f>
-        <v/>
-      </c>
-      <c r="I7" s="3">
-        <f>IF($E7, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M7, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T7, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O7, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N7, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P7, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F7, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L7, "Has Identity", "Has no Identity")</f>
+  $AO7,
+  $AD7,
+  $AE7,
+  $AF7,
+  $AG7,
+  $AH7,
+  $AI7,
+  $AJ7
+)</f>
         <v/>
       </c>
       <c r="J7" s="3">
+        <f>AND(
+  $I7,
+  $AK7,
+  $AL7
+)</f>
+        <v/>
+      </c>
+      <c r="K7" s="3">
+        <f>SUM(IF($AD7,1,0),
+IF($AE7,1,0),
+IF($AF7,1,0),
+IF($AG7,1,0),
+IF($AH7,1,0),
+IF($AI7,1,0),
+IF($AJ7,1,0),
+IF($AK7,1,0),
+IF($AL7,1,0),
+IF($AM7,1,0),
+IF($AN7,1,0))</f>
+        <v/>
+      </c>
+      <c r="L7" s="3">
+        <f>IF($E7, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P7, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W7, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R7, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q7, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S7, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F7, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O7, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M7" s="3">
         <f>IF(NOT($H7 = $C7),
   $B7 &amp; " " &amp; IF($H7, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C7, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V7, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
+  IF($C7, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y7, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L7" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M7" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N7" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O7" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P7" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="2" t="b">
         <v>1</v>
@@ -1230,34 +1742,80 @@
       <c r="S7" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T7" s="3">
-        <f>$U7 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U7" s="2" t="n">
+      <c r="T7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" s="3">
+        <f>$X7 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X7" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V7" s="3">
-        <f>AND($R7, $S7)</f>
-        <v/>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
+      <c r="Y7" s="3">
+        <f>AND($U7, $V7)</f>
+        <v/>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X7" s="3">
-        <f>IF($U7 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y7" s="2" t="inlineStr">
+      <c r="AA7" s="3">
+        <f>IF($X7 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z7" s="2" t="n">
+      <c r="AC7" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="AD7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1288,85 +1846,160 @@
         <v/>
       </c>
       <c r="H8" s="3">
+        <f>OR(
+  AND(
+    $E8,
+    $P8,
+    $W8,
+    $R8,
+    $Q8,
+    $S8,
+    NOT($F8),
+    NOT($O8)
+  ),
+  $K8 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I8" s="3">
         <f>AND(
-  $E8,
-  $M8,
-  $T8,
-  $O8,
-  $N8,
-  $P8,
-  NOT($F8),
-  NOT($L8)
-)</f>
-        <v/>
-      </c>
-      <c r="I8" s="3">
-        <f>IF($E8, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M8, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T8, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O8, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N8, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P8, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F8, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L8, "Has Identity", "Has no Identity")</f>
+  $AO8,
+  $AD8,
+  $AE8,
+  $AF8,
+  $AG8,
+  $AH8,
+  $AI8,
+  $AJ8
+)</f>
         <v/>
       </c>
       <c r="J8" s="3">
+        <f>AND(
+  $I8,
+  $AK8,
+  $AL8
+)</f>
+        <v/>
+      </c>
+      <c r="K8" s="3">
+        <f>SUM(IF($AD8,1,0),
+IF($AE8,1,0),
+IF($AF8,1,0),
+IF($AG8,1,0),
+IF($AH8,1,0),
+IF($AI8,1,0),
+IF($AJ8,1,0),
+IF($AK8,1,0),
+IF($AL8,1,0),
+IF($AM8,1,0),
+IF($AN8,1,0))</f>
+        <v/>
+      </c>
+      <c r="L8" s="3">
+        <f>IF($E8, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P8, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W8, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R8, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q8, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S8, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F8, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O8, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M8" s="3">
         <f>IF(NOT($H8 = $C8),
   $B8 &amp; " " &amp; IF($H8, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C8, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V8, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
+  IF($C8, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y8, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L8" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M8" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N8" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O8" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T8" s="3">
-        <f>$U8 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U8" s="2" t="n">
+      <c r="T8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" s="3">
+        <f>$X8 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X8" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V8" s="3">
-        <f>AND($R8, $S8)</f>
-        <v/>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
+      <c r="Y8" s="3">
+        <f>AND($U8, $V8)</f>
+        <v/>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X8" s="3">
-        <f>IF($U8 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y8" s="2" t="inlineStr">
+      <c r="AA8" s="3">
+        <f>IF($X8 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z8" s="2" t="n">
+      <c r="AC8" s="2" t="n">
         <v>7</v>
       </c>
+      <c r="AD8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -1397,85 +2030,160 @@
         <v/>
       </c>
       <c r="H9" s="3">
+        <f>OR(
+  AND(
+    $E9,
+    $P9,
+    $W9,
+    $R9,
+    $Q9,
+    $S9,
+    NOT($F9),
+    NOT($O9)
+  ),
+  $K9 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I9" s="3">
         <f>AND(
-  $E9,
-  $M9,
-  $T9,
-  $O9,
-  $N9,
-  $P9,
-  NOT($F9),
-  NOT($L9)
-)</f>
-        <v/>
-      </c>
-      <c r="I9" s="3">
-        <f>IF($E9, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M9, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T9, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O9, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N9, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P9, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F9, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L9, "Has Identity", "Has no Identity")</f>
+  $AO9,
+  $AD9,
+  $AE9,
+  $AF9,
+  $AG9,
+  $AH9,
+  $AI9,
+  $AJ9
+)</f>
         <v/>
       </c>
       <c r="J9" s="3">
+        <f>AND(
+  $I9,
+  $AK9,
+  $AL9
+)</f>
+        <v/>
+      </c>
+      <c r="K9" s="3">
+        <f>SUM(IF($AD9,1,0),
+IF($AE9,1,0),
+IF($AF9,1,0),
+IF($AG9,1,0),
+IF($AH9,1,0),
+IF($AI9,1,0),
+IF($AJ9,1,0),
+IF($AK9,1,0),
+IF($AL9,1,0),
+IF($AM9,1,0),
+IF($AN9,1,0))</f>
+        <v/>
+      </c>
+      <c r="L9" s="3">
+        <f>IF($E9, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P9, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W9, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R9, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q9, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S9, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F9, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O9, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M9" s="3">
         <f>IF(NOT($H9 = $C9),
   $B9 &amp; " " &amp; IF($H9, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C9, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V9, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
+  IF($C9, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y9, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M9" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N9" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S9" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T9" s="3">
-        <f>$U9 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V9" s="3">
-        <f>AND($R9, $S9)</f>
-        <v/>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W9" s="3">
+        <f>$X9 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="3">
+        <f>AND($U9, $V9)</f>
+        <v/>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X9" s="3">
-        <f>IF($U9 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y9" s="2" t="inlineStr">
+      <c r="AA9" s="3">
+        <f>IF($X9 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z9" s="2" t="n">
+      <c r="AC9" s="2" t="n">
         <v>8</v>
       </c>
+      <c r="AD9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1506,85 +2214,160 @@
         <v/>
       </c>
       <c r="H10" s="3">
+        <f>OR(
+  AND(
+    $E10,
+    $P10,
+    $W10,
+    $R10,
+    $Q10,
+    $S10,
+    NOT($F10),
+    NOT($O10)
+  ),
+  $K10 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I10" s="3">
         <f>AND(
-  $E10,
-  $M10,
-  $T10,
-  $O10,
-  $N10,
-  $P10,
-  NOT($F10),
-  NOT($L10)
-)</f>
-        <v/>
-      </c>
-      <c r="I10" s="3">
-        <f>IF($E10, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M10, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T10, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O10, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N10, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P10, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F10, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L10, "Has Identity", "Has no Identity")</f>
+  $AO10,
+  $AD10,
+  $AE10,
+  $AF10,
+  $AG10,
+  $AH10,
+  $AI10,
+  $AJ10
+)</f>
         <v/>
       </c>
       <c r="J10" s="3">
+        <f>AND(
+  $I10,
+  $AK10,
+  $AL10
+)</f>
+        <v/>
+      </c>
+      <c r="K10" s="3">
+        <f>SUM(IF($AD10,1,0),
+IF($AE10,1,0),
+IF($AF10,1,0),
+IF($AG10,1,0),
+IF($AH10,1,0),
+IF($AI10,1,0),
+IF($AJ10,1,0),
+IF($AK10,1,0),
+IF($AL10,1,0),
+IF($AM10,1,0),
+IF($AN10,1,0))</f>
+        <v/>
+      </c>
+      <c r="L10" s="3">
+        <f>IF($E10, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P10, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W10, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R10, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q10, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S10, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F10, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O10, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M10" s="3">
         <f>IF(NOT($H10 = $C10),
   $B10 &amp; " " &amp; IF($H10, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C10, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V10, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
+  IF($C10, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y10, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N10" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O10" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3">
-        <f>$U10 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W10" s="3">
+        <f>$X10 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X10" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V10" s="3">
-        <f>AND($R10, $S10)</f>
-        <v/>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
+      <c r="Y10" s="3">
+        <f>AND($U10, $V10)</f>
+        <v/>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X10" s="3">
-        <f>IF($U10 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y10" s="2" t="inlineStr">
+      <c r="AA10" s="3">
+        <f>IF($X10 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z10" s="2" t="n">
+      <c r="AC10" s="2" t="n">
         <v>9</v>
       </c>
+      <c r="AD10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1615,42 +2398,71 @@
         <v/>
       </c>
       <c r="H11" s="3">
+        <f>OR(
+  AND(
+    $E11,
+    $P11,
+    $W11,
+    $R11,
+    $Q11,
+    $S11,
+    NOT($F11),
+    NOT($O11)
+  ),
+  $K11 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I11" s="3">
         <f>AND(
-  $E11,
-  $M11,
-  $T11,
-  $O11,
-  $N11,
-  $P11,
-  NOT($F11),
-  NOT($L11)
-)</f>
-        <v/>
-      </c>
-      <c r="I11" s="3">
-        <f>IF($E11, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M11, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T11, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O11, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N11, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P11, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F11, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L11, "Has Identity", "Has no Identity")</f>
+  $AO11,
+  $AD11,
+  $AE11,
+  $AF11,
+  $AG11,
+  $AH11,
+  $AI11,
+  $AJ11
+)</f>
         <v/>
       </c>
       <c r="J11" s="3">
+        <f>AND(
+  $I11,
+  $AK11,
+  $AL11
+)</f>
+        <v/>
+      </c>
+      <c r="K11" s="3">
+        <f>SUM(IF($AD11,1,0),
+IF($AE11,1,0),
+IF($AF11,1,0),
+IF($AG11,1,0),
+IF($AH11,1,0),
+IF($AI11,1,0),
+IF($AJ11,1,0),
+IF($AK11,1,0),
+IF($AL11,1,0),
+IF($AM11,1,0),
+IF($AN11,1,0))</f>
+        <v/>
+      </c>
+      <c r="L11" s="3">
+        <f>IF($E11, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P11, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W11, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R11, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q11, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S11, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F11, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O11, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M11" s="3">
         <f>IF(NOT($H11 = $C11),
   $B11 &amp; " " &amp; IF($H11, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C11, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V11, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
+  IF($C11, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y11, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M11" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" s="2" t="b">
         <v>1</v>
       </c>
@@ -1661,39 +2473,85 @@
         <v>0</v>
       </c>
       <c r="R11" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S11" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T11" s="3">
-        <f>$U11 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V11" s="3">
-        <f>AND($R11, $S11)</f>
-        <v/>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V11" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W11" s="3">
+        <f>$X11 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="3">
+        <f>AND($U11, $V11)</f>
+        <v/>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X11" s="3">
-        <f>IF($U11 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y11" s="2" t="inlineStr">
+      <c r="AA11" s="3">
+        <f>IF($X11 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z11" s="2" t="n">
+      <c r="AC11" s="2" t="n">
         <v>10</v>
       </c>
+      <c r="AD11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1724,85 +2582,160 @@
         <v/>
       </c>
       <c r="H12" s="3">
+        <f>OR(
+  AND(
+    $E12,
+    $P12,
+    $W12,
+    $R12,
+    $Q12,
+    $S12,
+    NOT($F12),
+    NOT($O12)
+  ),
+  $K12 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I12" s="3">
         <f>AND(
-  $E12,
-  $M12,
-  $T12,
-  $O12,
-  $N12,
-  $P12,
-  NOT($F12),
-  NOT($L12)
-)</f>
-        <v/>
-      </c>
-      <c r="I12" s="3">
-        <f>IF($E12, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M12, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T12, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O12, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N12, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P12, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F12, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L12, "Has Identity", "Has no Identity")</f>
+  $AO12,
+  $AD12,
+  $AE12,
+  $AF12,
+  $AG12,
+  $AH12,
+  $AI12,
+  $AJ12
+)</f>
         <v/>
       </c>
       <c r="J12" s="3">
+        <f>AND(
+  $I12,
+  $AK12,
+  $AL12
+)</f>
+        <v/>
+      </c>
+      <c r="K12" s="3">
+        <f>SUM(IF($AD12,1,0),
+IF($AE12,1,0),
+IF($AF12,1,0),
+IF($AG12,1,0),
+IF($AH12,1,0),
+IF($AI12,1,0),
+IF($AJ12,1,0),
+IF($AK12,1,0),
+IF($AL12,1,0),
+IF($AM12,1,0),
+IF($AN12,1,0))</f>
+        <v/>
+      </c>
+      <c r="L12" s="3">
+        <f>IF($E12, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P12, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W12, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R12, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q12, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S12, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F12, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O12, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M12" s="3">
         <f>IF(NOT($H12 = $C12),
   $B12 &amp; " " &amp; IF($H12, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C12, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V12, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
+  IF($C12, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y12, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N12" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O12" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q12" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" s="2" t="b">
         <v>1</v>
       </c>
       <c r="S12" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T12" s="3">
-        <f>$U12 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U12" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W12" s="3">
+        <f>$X12 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X12" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V12" s="3">
-        <f>AND($R12, $S12)</f>
-        <v/>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
+      <c r="Y12" s="3">
+        <f>AND($U12, $V12)</f>
+        <v/>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X12" s="3">
-        <f>IF($U12 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y12" s="2" t="inlineStr">
+      <c r="AA12" s="3">
+        <f>IF($X12 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z12" s="2" t="n">
+      <c r="AC12" s="2" t="n">
         <v>11</v>
       </c>
+      <c r="AD12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1833,85 +2766,160 @@
         <v/>
       </c>
       <c r="H13" s="3">
+        <f>OR(
+  AND(
+    $E13,
+    $P13,
+    $W13,
+    $R13,
+    $Q13,
+    $S13,
+    NOT($F13),
+    NOT($O13)
+  ),
+  $K13 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I13" s="3">
         <f>AND(
-  $E13,
-  $M13,
-  $T13,
-  $O13,
-  $N13,
-  $P13,
-  NOT($F13),
-  NOT($L13)
-)</f>
-        <v/>
-      </c>
-      <c r="I13" s="3">
-        <f>IF($E13, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M13, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T13, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O13, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N13, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P13, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F13, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L13, "Has Identity", "Has no Identity")</f>
+  $AO13,
+  $AD13,
+  $AE13,
+  $AF13,
+  $AG13,
+  $AH13,
+  $AI13,
+  $AJ13
+)</f>
         <v/>
       </c>
       <c r="J13" s="3">
+        <f>AND(
+  $I13,
+  $AK13,
+  $AL13
+)</f>
+        <v/>
+      </c>
+      <c r="K13" s="3">
+        <f>SUM(IF($AD13,1,0),
+IF($AE13,1,0),
+IF($AF13,1,0),
+IF($AG13,1,0),
+IF($AH13,1,0),
+IF($AI13,1,0),
+IF($AJ13,1,0),
+IF($AK13,1,0),
+IF($AL13,1,0),
+IF($AM13,1,0),
+IF($AN13,1,0))</f>
+        <v/>
+      </c>
+      <c r="L13" s="3">
+        <f>IF($E13, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P13, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W13, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R13, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q13, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S13, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F13, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O13, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M13" s="3">
         <f>IF(NOT($H13 = $C13),
   $B13 &amp; " " &amp; IF($H13, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C13, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V13, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+  IF($C13, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y13, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N13" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" s="2" t="b">
         <v>1</v>
       </c>
       <c r="P13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="T13" s="3">
-        <f>$U13 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V13" s="3">
-        <f>AND($R13, $S13)</f>
-        <v/>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="T13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V13" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W13" s="3">
+        <f>$X13 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="3">
+        <f>AND($U13, $V13)</f>
+        <v/>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X13" s="3">
-        <f>IF($U13 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y13" s="2" t="inlineStr">
+      <c r="AA13" s="3">
+        <f>IF($X13 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z13" s="2" t="n">
+      <c r="AC13" s="2" t="n">
         <v>12</v>
       </c>
+      <c r="AD13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1942,85 +2950,160 @@
         <v/>
       </c>
       <c r="H14" s="3">
+        <f>OR(
+  AND(
+    $E14,
+    $P14,
+    $W14,
+    $R14,
+    $Q14,
+    $S14,
+    NOT($F14),
+    NOT($O14)
+  ),
+  $K14 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I14" s="3">
         <f>AND(
-  $E14,
-  $M14,
-  $T14,
-  $O14,
-  $N14,
-  $P14,
-  NOT($F14),
-  NOT($L14)
-)</f>
-        <v/>
-      </c>
-      <c r="I14" s="3">
-        <f>IF($E14, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M14, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T14, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O14, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N14, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P14, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F14, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L14, "Has Identity", "Has no Identity")</f>
+  $AO14,
+  $AD14,
+  $AE14,
+  $AF14,
+  $AG14,
+  $AH14,
+  $AI14,
+  $AJ14
+)</f>
         <v/>
       </c>
       <c r="J14" s="3">
+        <f>AND(
+  $I14,
+  $AK14,
+  $AL14
+)</f>
+        <v/>
+      </c>
+      <c r="K14" s="3">
+        <f>SUM(IF($AD14,1,0),
+IF($AE14,1,0),
+IF($AF14,1,0),
+IF($AG14,1,0),
+IF($AH14,1,0),
+IF($AI14,1,0),
+IF($AJ14,1,0),
+IF($AK14,1,0),
+IF($AL14,1,0),
+IF($AM14,1,0),
+IF($AN14,1,0))</f>
+        <v/>
+      </c>
+      <c r="L14" s="3">
+        <f>IF($E14, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P14, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W14, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R14, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q14, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S14, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F14, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O14, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M14" s="3">
         <f>IF(NOT($H14 = $C14),
   $B14 &amp; " " &amp; IF($H14, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C14, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V14, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
+  IF($C14, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y14, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N14" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O14" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3">
-        <f>$U14 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
+        <f>$X14 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X14" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V14" s="3">
-        <f>AND($R14, $S14)</f>
-        <v/>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
+      <c r="Y14" s="3">
+        <f>AND($U14, $V14)</f>
+        <v/>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X14" s="3">
-        <f>IF($U14 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y14" s="2" t="inlineStr">
+      <c r="AA14" s="3">
+        <f>IF($X14 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z14" s="2" t="n">
+      <c r="AC14" s="2" t="n">
         <v>13</v>
       </c>
+      <c r="AD14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -2051,42 +3134,71 @@
         <v/>
       </c>
       <c r="H15" s="3">
+        <f>OR(
+  AND(
+    $E15,
+    $P15,
+    $W15,
+    $R15,
+    $Q15,
+    $S15,
+    NOT($F15),
+    NOT($O15)
+  ),
+  $K15 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I15" s="3">
         <f>AND(
-  $E15,
-  $M15,
-  $T15,
-  $O15,
-  $N15,
-  $P15,
-  NOT($F15),
-  NOT($L15)
-)</f>
-        <v/>
-      </c>
-      <c r="I15" s="3">
-        <f>IF($E15, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M15, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T15, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O15, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N15, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P15, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F15, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L15, "Has Identity", "Has no Identity")</f>
+  $AO15,
+  $AD15,
+  $AE15,
+  $AF15,
+  $AG15,
+  $AH15,
+  $AI15,
+  $AJ15
+)</f>
         <v/>
       </c>
       <c r="J15" s="3">
+        <f>AND(
+  $I15,
+  $AK15,
+  $AL15
+)</f>
+        <v/>
+      </c>
+      <c r="K15" s="3">
+        <f>SUM(IF($AD15,1,0),
+IF($AE15,1,0),
+IF($AF15,1,0),
+IF($AG15,1,0),
+IF($AH15,1,0),
+IF($AI15,1,0),
+IF($AJ15,1,0),
+IF($AK15,1,0),
+IF($AL15,1,0),
+IF($AM15,1,0),
+IF($AN15,1,0))</f>
+        <v/>
+      </c>
+      <c r="L15" s="3">
+        <f>IF($E15, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P15, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W15, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R15, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q15, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S15, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F15, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O15, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M15" s="3">
         <f>IF(NOT($H15 = $C15),
   $B15 &amp; " " &amp; IF($H15, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C15, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V15, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
+  IF($C15, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y15, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M15" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N15" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O15" s="2" t="b">
         <v>0</v>
       </c>
@@ -2102,34 +3214,80 @@
       <c r="S15" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T15" s="3">
-        <f>$U15 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V15" s="3">
-        <f>AND($R15, $S15)</f>
-        <v/>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
+      <c r="T15" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W15" s="3">
+        <f>$X15 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="3">
+        <f>AND($U15, $V15)</f>
+        <v/>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X15" s="3">
-        <f>IF($U15 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y15" s="2" t="inlineStr">
+      <c r="AA15" s="3">
+        <f>IF($X15 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z15" s="2" t="n">
+      <c r="AC15" s="2" t="n">
         <v>14</v>
       </c>
+      <c r="AD15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -2160,85 +3318,160 @@
         <v/>
       </c>
       <c r="H16" s="3">
+        <f>OR(
+  AND(
+    $E16,
+    $P16,
+    $W16,
+    $R16,
+    $Q16,
+    $S16,
+    NOT($F16),
+    NOT($O16)
+  ),
+  $K16 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I16" s="3">
         <f>AND(
-  $E16,
-  $M16,
-  $T16,
-  $O16,
-  $N16,
-  $P16,
-  NOT($F16),
-  NOT($L16)
-)</f>
-        <v/>
-      </c>
-      <c r="I16" s="3">
-        <f>IF($E16, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M16, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T16, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O16, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N16, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P16, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F16, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L16, "Has Identity", "Has no Identity")</f>
+  $AO16,
+  $AD16,
+  $AE16,
+  $AF16,
+  $AG16,
+  $AH16,
+  $AI16,
+  $AJ16
+)</f>
         <v/>
       </c>
       <c r="J16" s="3">
+        <f>AND(
+  $I16,
+  $AK16,
+  $AL16
+)</f>
+        <v/>
+      </c>
+      <c r="K16" s="3">
+        <f>SUM(IF($AD16,1,0),
+IF($AE16,1,0),
+IF($AF16,1,0),
+IF($AG16,1,0),
+IF($AH16,1,0),
+IF($AI16,1,0),
+IF($AJ16,1,0),
+IF($AK16,1,0),
+IF($AL16,1,0),
+IF($AM16,1,0),
+IF($AN16,1,0))</f>
+        <v/>
+      </c>
+      <c r="L16" s="3">
+        <f>IF($E16, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P16, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W16, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R16, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q16, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S16, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F16, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O16, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M16" s="3">
         <f>IF(NOT($H16 = $C16),
   $B16 &amp; " " &amp; IF($H16, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C16, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V16, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
+  IF($C16, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y16, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M16" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N16" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O16" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T16" s="3">
-        <f>$U16 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W16" s="3">
+        <f>$X16 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X16" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V16" s="3">
-        <f>AND($R16, $S16)</f>
-        <v/>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="Y16" s="3">
+        <f>AND($U16, $V16)</f>
+        <v/>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X16" s="3">
-        <f>IF($U16 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y16" s="2" t="inlineStr">
+      <c r="AA16" s="3">
+        <f>IF($X16 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z16" s="2" t="n">
+      <c r="AC16" s="2" t="n">
         <v>15</v>
       </c>
+      <c r="AD16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -2269,85 +3502,160 @@
         <v/>
       </c>
       <c r="H17" s="3">
+        <f>OR(
+  AND(
+    $E17,
+    $P17,
+    $W17,
+    $R17,
+    $Q17,
+    $S17,
+    NOT($F17),
+    NOT($O17)
+  ),
+  $K17 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I17" s="3">
         <f>AND(
-  $E17,
-  $M17,
-  $T17,
-  $O17,
-  $N17,
-  $P17,
-  NOT($F17),
-  NOT($L17)
-)</f>
-        <v/>
-      </c>
-      <c r="I17" s="3">
-        <f>IF($E17, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M17, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T17, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O17, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N17, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P17, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F17, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L17, "Has Identity", "Has no Identity")</f>
+  $AO17,
+  $AD17,
+  $AE17,
+  $AF17,
+  $AG17,
+  $AH17,
+  $AI17,
+  $AJ17
+)</f>
         <v/>
       </c>
       <c r="J17" s="3">
+        <f>AND(
+  $I17,
+  $AK17,
+  $AL17
+)</f>
+        <v/>
+      </c>
+      <c r="K17" s="3">
+        <f>SUM(IF($AD17,1,0),
+IF($AE17,1,0),
+IF($AF17,1,0),
+IF($AG17,1,0),
+IF($AH17,1,0),
+IF($AI17,1,0),
+IF($AJ17,1,0),
+IF($AK17,1,0),
+IF($AL17,1,0),
+IF($AM17,1,0),
+IF($AN17,1,0))</f>
+        <v/>
+      </c>
+      <c r="L17" s="3">
+        <f>IF($E17, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P17, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W17, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R17, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q17, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S17, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F17, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O17, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M17" s="3">
         <f>IF(NOT($H17 = $C17),
   $B17 &amp; " " &amp; IF($H17, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C17, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V17, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
+  IF($C17, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y17, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N17" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="P17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17" s="2" t="b">
         <v>0</v>
       </c>
       <c r="S17" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3">
-        <f>$U17 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V17" s="3">
-        <f>AND($R17, $S17)</f>
-        <v/>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T17" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="U17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W17" s="3">
+        <f>$X17 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="3">
+        <f>AND($U17, $V17)</f>
+        <v/>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X17" s="3">
-        <f>IF($U17 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="AA17" s="3">
+        <f>IF($X17 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>M4</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="n">
+      <c r="AC17" s="2" t="n">
         <v>16</v>
       </c>
+      <c r="AD17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -2378,85 +3686,160 @@
         <v/>
       </c>
       <c r="H18" s="3">
+        <f>OR(
+  AND(
+    $E18,
+    $P18,
+    $W18,
+    $R18,
+    $Q18,
+    $S18,
+    NOT($F18),
+    NOT($O18)
+  ),
+  $K18 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I18" s="3">
         <f>AND(
-  $E18,
-  $M18,
-  $T18,
-  $O18,
-  $N18,
-  $P18,
-  NOT($F18),
-  NOT($L18)
-)</f>
-        <v/>
-      </c>
-      <c r="I18" s="3">
-        <f>IF($E18, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M18, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T18, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O18, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N18, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P18, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F18, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L18, "Has Identity", "Has no Identity")</f>
+  $AO18,
+  $AD18,
+  $AE18,
+  $AF18,
+  $AG18,
+  $AH18,
+  $AI18,
+  $AJ18
+)</f>
         <v/>
       </c>
       <c r="J18" s="3">
+        <f>AND(
+  $I18,
+  $AK18,
+  $AL18
+)</f>
+        <v/>
+      </c>
+      <c r="K18" s="3">
+        <f>SUM(IF($AD18,1,0),
+IF($AE18,1,0),
+IF($AF18,1,0),
+IF($AG18,1,0),
+IF($AH18,1,0),
+IF($AI18,1,0),
+IF($AJ18,1,0),
+IF($AK18,1,0),
+IF($AL18,1,0),
+IF($AM18,1,0),
+IF($AN18,1,0))</f>
+        <v/>
+      </c>
+      <c r="L18" s="3">
+        <f>IF($E18, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P18, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W18, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R18, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q18, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S18, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F18, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O18, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M18" s="3">
         <f>IF(NOT($H18 = $C18),
   $B18 &amp; " " &amp; IF($H18, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C18, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V18, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+  IF($C18, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y18, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>Natural Language</t>
         </is>
       </c>
-      <c r="L18" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M18" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O18" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P18" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S18" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T18" s="3">
-        <f>$U18 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U18" s="2" t="n">
+      <c r="T18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W18" s="3">
+        <f>$X18 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X18" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="3">
-        <f>AND($R18, $S18)</f>
-        <v/>
-      </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="Y18" s="3">
+        <f>AND($U18, $V18)</f>
+        <v/>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X18" s="3">
-        <f>IF($U18 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y18" s="2" t="inlineStr">
+      <c r="AA18" s="3">
+        <f>IF($X18 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z18" s="2" t="n">
+      <c r="AC18" s="2" t="n">
         <v>17</v>
       </c>
+      <c r="AD18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -2487,50 +3870,79 @@
         <v/>
       </c>
       <c r="H19" s="3">
+        <f>OR(
+  AND(
+    $E19,
+    $P19,
+    $W19,
+    $R19,
+    $Q19,
+    $S19,
+    NOT($F19),
+    NOT($O19)
+  ),
+  $K19 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I19" s="3">
         <f>AND(
-  $E19,
-  $M19,
-  $T19,
-  $O19,
-  $N19,
-  $P19,
-  NOT($F19),
-  NOT($L19)
-)</f>
-        <v/>
-      </c>
-      <c r="I19" s="3">
-        <f>IF($E19, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M19, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T19, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O19, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N19, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P19, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F19, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L19, "Has Identity", "Has no Identity")</f>
+  $AO19,
+  $AD19,
+  $AE19,
+  $AF19,
+  $AG19,
+  $AH19,
+  $AI19,
+  $AJ19
+)</f>
         <v/>
       </c>
       <c r="J19" s="3">
+        <f>AND(
+  $I19,
+  $AK19,
+  $AL19
+)</f>
+        <v/>
+      </c>
+      <c r="K19" s="3">
+        <f>SUM(IF($AD19,1,0),
+IF($AE19,1,0),
+IF($AF19,1,0),
+IF($AG19,1,0),
+IF($AH19,1,0),
+IF($AI19,1,0),
+IF($AJ19,1,0),
+IF($AK19,1,0),
+IF($AL19,1,0),
+IF($AM19,1,0),
+IF($AN19,1,0))</f>
+        <v/>
+      </c>
+      <c r="L19" s="3">
+        <f>IF($E19, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P19, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W19, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R19, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q19, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S19, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F19, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O19, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M19" s="3">
         <f>IF(NOT($H19 = $C19),
   $B19 &amp; " " &amp; IF($H19, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C19, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V19, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
+  IF($C19, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y19, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>Physical event</t>
         </is>
       </c>
-      <c r="L19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M19" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N19" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19" s="2" t="b">
         <v>0</v>
@@ -2538,34 +3950,80 @@
       <c r="S19" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T19" s="3">
-        <f>$U19 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V19" s="3">
-        <f>AND($R19, $S19)</f>
-        <v/>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W19" s="3">
+        <f>$X19 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="3">
+        <f>AND($U19, $V19)</f>
+        <v/>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X19" s="3">
-        <f>IF($U19 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="AA19" s="3">
+        <f>IF($X19 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="AC19" s="2" t="n">
         <v>18</v>
       </c>
+      <c r="AD19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -2596,85 +4054,160 @@
         <v/>
       </c>
       <c r="H20" s="3">
+        <f>OR(
+  AND(
+    $E20,
+    $P20,
+    $W20,
+    $R20,
+    $Q20,
+    $S20,
+    NOT($F20),
+    NOT($O20)
+  ),
+  $K20 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I20" s="3">
         <f>AND(
-  $E20,
-  $M20,
-  $T20,
-  $O20,
-  $N20,
-  $P20,
-  NOT($F20),
-  NOT($L20)
-)</f>
-        <v/>
-      </c>
-      <c r="I20" s="3">
-        <f>IF($E20, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M20, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T20, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O20, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N20, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P20, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F20, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L20, "Has Identity", "Has no Identity")</f>
+  $AO20,
+  $AD20,
+  $AE20,
+  $AF20,
+  $AG20,
+  $AH20,
+  $AI20,
+  $AJ20
+)</f>
         <v/>
       </c>
       <c r="J20" s="3">
+        <f>AND(
+  $I20,
+  $AK20,
+  $AL20
+)</f>
+        <v/>
+      </c>
+      <c r="K20" s="3">
+        <f>SUM(IF($AD20,1,0),
+IF($AE20,1,0),
+IF($AF20,1,0),
+IF($AG20,1,0),
+IF($AH20,1,0),
+IF($AI20,1,0),
+IF($AJ20,1,0),
+IF($AK20,1,0),
+IF($AL20,1,0),
+IF($AM20,1,0),
+IF($AN20,1,0))</f>
+        <v/>
+      </c>
+      <c r="L20" s="3">
+        <f>IF($E20, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P20, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W20, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R20, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q20, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S20, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F20, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O20, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M20" s="3">
         <f>IF(NOT($H20 = $C20),
   $B20 &amp; " " &amp; IF($H20, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C20, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V20, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
+  IF($C20, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y20, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N20" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O20" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S20" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T20" s="3">
-        <f>$U20 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
+        <f>$X20 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X20" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V20" s="3">
-        <f>AND($R20, $S20)</f>
-        <v/>
-      </c>
-      <c r="W20" s="2" t="inlineStr">
+      <c r="Y20" s="3">
+        <f>AND($U20, $V20)</f>
+        <v/>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X20" s="3">
-        <f>IF($U20 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y20" s="2" t="inlineStr">
+      <c r="AA20" s="3">
+        <f>IF($X20 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z20" s="2" t="n">
+      <c r="AC20" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="AD20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -2705,47 +4238,76 @@
         <v/>
       </c>
       <c r="H21" s="3">
+        <f>OR(
+  AND(
+    $E21,
+    $P21,
+    $W21,
+    $R21,
+    $Q21,
+    $S21,
+    NOT($F21),
+    NOT($O21)
+  ),
+  $K21 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I21" s="3">
         <f>AND(
-  $E21,
-  $M21,
-  $T21,
-  $O21,
-  $N21,
-  $P21,
-  NOT($F21),
-  NOT($L21)
-)</f>
-        <v/>
-      </c>
-      <c r="I21" s="3">
-        <f>IF($E21, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M21, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T21, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O21, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N21, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P21, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F21, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L21, "Has Identity", "Has no Identity")</f>
+  $AO21,
+  $AD21,
+  $AE21,
+  $AF21,
+  $AG21,
+  $AH21,
+  $AI21,
+  $AJ21
+)</f>
         <v/>
       </c>
       <c r="J21" s="3">
+        <f>AND(
+  $I21,
+  $AK21,
+  $AL21
+)</f>
+        <v/>
+      </c>
+      <c r="K21" s="3">
+        <f>SUM(IF($AD21,1,0),
+IF($AE21,1,0),
+IF($AF21,1,0),
+IF($AG21,1,0),
+IF($AH21,1,0),
+IF($AI21,1,0),
+IF($AJ21,1,0),
+IF($AK21,1,0),
+IF($AL21,1,0),
+IF($AM21,1,0),
+IF($AN21,1,0))</f>
+        <v/>
+      </c>
+      <c r="L21" s="3">
+        <f>IF($E21, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P21, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W21, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R21, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q21, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S21, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F21, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O21, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M21" s="3">
         <f>IF(NOT($H21 = $C21),
   $B21 &amp; " " &amp; IF($H21, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C21, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V21, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
+  IF($C21, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y21, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>Physical Object</t>
         </is>
       </c>
-      <c r="L21" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="N21" s="2" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P21" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="2" t="b">
         <v>0</v>
@@ -2754,36 +4316,82 @@
         <v>0</v>
       </c>
       <c r="S21" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T21" s="3">
-        <f>$U21 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U21" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" s="3">
-        <f>AND($R21, $S21)</f>
-        <v/>
-      </c>
-      <c r="W21" s="2" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W21" s="3">
+        <f>$X21 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="3">
+        <f>AND($U21, $V21)</f>
+        <v/>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="X21" s="3">
-        <f>IF($U21 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y21" s="2" t="inlineStr">
+      <c r="AA21" s="3">
+        <f>IF($X21 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="Z21" s="2" t="n">
+      <c r="AC21" s="2" t="n">
         <v>20</v>
       </c>
+      <c r="AD21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -2814,85 +4422,160 @@
         <v/>
       </c>
       <c r="H22" s="3">
+        <f>OR(
+  AND(
+    $E22,
+    $P22,
+    $W22,
+    $R22,
+    $Q22,
+    $S22,
+    NOT($F22),
+    NOT($O22)
+  ),
+  $K22 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I22" s="3">
         <f>AND(
-  $E22,
-  $M22,
-  $T22,
-  $O22,
-  $N22,
-  $P22,
-  NOT($F22),
-  NOT($L22)
-)</f>
-        <v/>
-      </c>
-      <c r="I22" s="3">
-        <f>IF($E22, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M22, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T22, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O22, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N22, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P22, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F22, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L22, "Has Identity", "Has no Identity")</f>
+  $AO22,
+  $AD22,
+  $AE22,
+  $AF22,
+  $AG22,
+  $AH22,
+  $AI22,
+  $AJ22
+)</f>
         <v/>
       </c>
       <c r="J22" s="3">
+        <f>AND(
+  $I22,
+  $AK22,
+  $AL22
+)</f>
+        <v/>
+      </c>
+      <c r="K22" s="3">
+        <f>SUM(IF($AD22,1,0),
+IF($AE22,1,0),
+IF($AF22,1,0),
+IF($AG22,1,0),
+IF($AH22,1,0),
+IF($AI22,1,0),
+IF($AJ22,1,0),
+IF($AK22,1,0),
+IF($AL22,1,0),
+IF($AM22,1,0),
+IF($AN22,1,0))</f>
+        <v/>
+      </c>
+      <c r="L22" s="3">
+        <f>IF($E22, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P22, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W22, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R22, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q22, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S22, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F22, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O22, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M22" s="3">
         <f>IF(NOT($H22 = $C22),
   $B22 &amp; " " &amp; IF($H22, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C22, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V22, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
+  IF($C22, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y22, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>Formal Language</t>
         </is>
       </c>
-      <c r="L22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M22" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N22" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O22" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R22" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S22" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="T22" s="3">
-        <f>$U22 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W22" s="3">
+        <f>$X22 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X22" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V22" s="3">
-        <f>AND($R22, $S22)</f>
-        <v/>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
+      <c r="Y22" s="3">
+        <f>AND($U22, $V22)</f>
+        <v/>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X22" s="3">
-        <f>IF($U22 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y22" s="2" t="inlineStr">
+      <c r="AA22" s="3">
+        <f>IF($X22 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>M2</t>
         </is>
       </c>
-      <c r="Z22" s="2" t="n">
+      <c r="AC22" s="2" t="n">
         <v>21</v>
       </c>
+      <c r="AD22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -2923,50 +4606,79 @@
         <v/>
       </c>
       <c r="H23" s="3">
+        <f>OR(
+  AND(
+    $E23,
+    $P23,
+    $W23,
+    $R23,
+    $Q23,
+    $S23,
+    NOT($F23),
+    NOT($O23)
+  ),
+  $K23 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I23" s="3">
         <f>AND(
-  $E23,
-  $M23,
-  $T23,
-  $O23,
-  $N23,
-  $P23,
-  NOT($F23),
-  NOT($L23)
-)</f>
-        <v/>
-      </c>
-      <c r="I23" s="3">
-        <f>IF($E23, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M23, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T23, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O23, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N23, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P23, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F23, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L23, "Has Identity", "Has no Identity")</f>
+  $AO23,
+  $AD23,
+  $AE23,
+  $AF23,
+  $AG23,
+  $AH23,
+  $AI23,
+  $AJ23
+)</f>
         <v/>
       </c>
       <c r="J23" s="3">
+        <f>AND(
+  $I23,
+  $AK23,
+  $AL23
+)</f>
+        <v/>
+      </c>
+      <c r="K23" s="3">
+        <f>SUM(IF($AD23,1,0),
+IF($AE23,1,0),
+IF($AF23,1,0),
+IF($AG23,1,0),
+IF($AH23,1,0),
+IF($AI23,1,0),
+IF($AJ23,1,0),
+IF($AK23,1,0),
+IF($AL23,1,0),
+IF($AM23,1,0),
+IF($AN23,1,0))</f>
+        <v/>
+      </c>
+      <c r="L23" s="3">
+        <f>IF($E23, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P23, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W23, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R23, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q23, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S23, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F23, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O23, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M23" s="3">
         <f>IF(NOT($H23 = $C23),
   $B23 &amp; " " &amp; IF($H23, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C23, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V23, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
+  IF($C23, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y23, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>Running Software</t>
         </is>
       </c>
-      <c r="L23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M23" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N23" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R23" s="2" t="b">
         <v>0</v>
@@ -2974,34 +4686,80 @@
       <c r="S23" s="2" t="b">
         <v>0</v>
       </c>
-      <c r="T23" s="3">
-        <f>$U23 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U23" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="V23" s="3">
-        <f>AND($R23, $S23)</f>
-        <v/>
-      </c>
-      <c r="W23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W23" s="3">
+        <f>$X23 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="3">
+        <f>AND($U23, $V23)</f>
+        <v/>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
         <is>
           <t>MultiDimensionalNonSymbolic</t>
         </is>
       </c>
-      <c r="X23" s="3">
-        <f>IF($U23 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y23" s="2" t="inlineStr">
+      <c r="AA23" s="3">
+        <f>IF($X23 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z23" s="2" t="n">
+      <c r="AC23" s="2" t="n">
         <v>22</v>
       </c>
+      <c r="AD23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -3032,50 +4790,79 @@
         <v/>
       </c>
       <c r="H24" s="3">
+        <f>OR(
+  AND(
+    $E24,
+    $P24,
+    $W24,
+    $R24,
+    $Q24,
+    $S24,
+    NOT($F24),
+    NOT($O24)
+  ),
+  $K24 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I24" s="3">
         <f>AND(
-  $E24,
-  $M24,
-  $T24,
-  $O24,
-  $N24,
-  $P24,
-  NOT($F24),
-  NOT($L24)
-)</f>
-        <v/>
-      </c>
-      <c r="I24" s="3">
-        <f>IF($E24, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($M24, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($T24, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($O24, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($N24, "Resolves to AST", "No AST") &amp; ", " &amp; IF($P24, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F24, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($L24, "Has Identity", "Has no Identity")</f>
+  $AO24,
+  $AD24,
+  $AE24,
+  $AF24,
+  $AG24,
+  $AH24,
+  $AI24,
+  $AJ24
+)</f>
         <v/>
       </c>
       <c r="J24" s="3">
+        <f>AND(
+  $I24,
+  $AK24,
+  $AL24
+)</f>
+        <v/>
+      </c>
+      <c r="K24" s="3">
+        <f>SUM(IF($AD24,1,0),
+IF($AE24,1,0),
+IF($AF24,1,0),
+IF($AG24,1,0),
+IF($AH24,1,0),
+IF($AI24,1,0),
+IF($AJ24,1,0),
+IF($AK24,1,0),
+IF($AL24,1,0),
+IF($AM24,1,0),
+IF($AN24,1,0))</f>
+        <v/>
+      </c>
+      <c r="L24" s="3">
+        <f>IF($E24, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P24, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W24, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R24, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q24, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S24, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F24, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O24, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M24" s="3">
         <f>IF(NOT($H24 = $C24),
   $B24 &amp; " " &amp; IF($H24, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
-  IF($C24, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($V24, " - Open World vs. Closed World Conflict.", "")</f>
-        <v/>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
+  IF($C24, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y24, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>MISSING: Have you seen this Language?</t>
         </is>
       </c>
-      <c r="L24" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="M24" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="N24" s="2" t="b">
-        <v>1</v>
-      </c>
       <c r="O24" s="2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P24" s="2" t="b">
         <v>1</v>
       </c>
       <c r="Q24" s="2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R24" s="2" t="b">
         <v>1</v>
@@ -3083,34 +4870,1868 @@
       <c r="S24" s="2" t="b">
         <v>1</v>
       </c>
-      <c r="T24" s="3">
-        <f>$U24 &gt; 1</f>
-        <v/>
-      </c>
-      <c r="U24" s="2" t="n">
+      <c r="T24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="V24" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W24" s="3">
+        <f>$X24 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X24" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="V24" s="3">
-        <f>AND($R24, $S24)</f>
-        <v/>
-      </c>
-      <c r="W24" s="2" t="inlineStr">
+      <c r="Y24" s="3">
+        <f>AND($U24, $V24)</f>
+        <v/>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
         <is>
           <t>OneDimensionalSymbolic</t>
         </is>
       </c>
-      <c r="X24" s="3">
-        <f>IF($U24 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
-        <v/>
-      </c>
-      <c r="Y24" s="2" t="inlineStr">
+      <c r="AA24" s="3">
+        <f>IF($X24 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
         <is>
           <t>M1</t>
         </is>
       </c>
-      <c r="Z24" s="2" t="n">
+      <c r="AC24" s="2" t="n">
         <v>23</v>
       </c>
+      <c r="AD24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>honeybee-waggle-dance</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Honeybee Waggle Dance</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="3">
+        <f>$E25 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3">
+        <f>"Is " &amp; $B25 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H25" s="3">
+        <f>OR(
+  AND(
+    $E25,
+    $P25,
+    $W25,
+    $R25,
+    $Q25,
+    $S25,
+    NOT($F25),
+    NOT($O25)
+  ),
+  $K25 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I25" s="3">
+        <f>AND(
+  $AO25,
+  $AD25,
+  $AE25,
+  $AF25,
+  $AG25,
+  $AH25,
+  $AI25,
+  $AJ25
+)</f>
+        <v/>
+      </c>
+      <c r="J25" s="3">
+        <f>AND(
+  $I25,
+  $AK25,
+  $AL25
+)</f>
+        <v/>
+      </c>
+      <c r="K25" s="3">
+        <f>SUM(IF($AD25,1,0),
+IF($AE25,1,0),
+IF($AF25,1,0),
+IF($AG25,1,0),
+IF($AH25,1,0),
+IF($AI25,1,0),
+IF($AJ25,1,0),
+IF($AK25,1,0),
+IF($AL25,1,0),
+IF($AM25,1,0),
+IF($AN25,1,0))</f>
+        <v/>
+      </c>
+      <c r="L25" s="3">
+        <f>IF($E25, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P25, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W25, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R25, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q25, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S25, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F25, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O25, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M25" s="3">
+        <f>IF(NOT($H25 = $C25),
+  $B25 &amp; " " &amp; IF($H25, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C25, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y25, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W25" s="3">
+        <f>$X25 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <f>AND($U25, $V25)</f>
+        <v/>
+      </c>
+      <c r="Z25" s="2" t="inlineStr"/>
+      <c r="AA25" s="3">
+        <f>IF($X25 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM25" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO25" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP25" s="2" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>vervet-monkey-alarm-calls</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Vervet Monkey Alarm Calls</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="3">
+        <f>$E26 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3">
+        <f>"Is " &amp; $B26 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H26" s="3">
+        <f>OR(
+  AND(
+    $E26,
+    $P26,
+    $W26,
+    $R26,
+    $Q26,
+    $S26,
+    NOT($F26),
+    NOT($O26)
+  ),
+  $K26 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I26" s="3">
+        <f>AND(
+  $AO26,
+  $AD26,
+  $AE26,
+  $AF26,
+  $AG26,
+  $AH26,
+  $AI26,
+  $AJ26
+)</f>
+        <v/>
+      </c>
+      <c r="J26" s="3">
+        <f>AND(
+  $I26,
+  $AK26,
+  $AL26
+)</f>
+        <v/>
+      </c>
+      <c r="K26" s="3">
+        <f>SUM(IF($AD26,1,0),
+IF($AE26,1,0),
+IF($AF26,1,0),
+IF($AG26,1,0),
+IF($AH26,1,0),
+IF($AI26,1,0),
+IF($AJ26,1,0),
+IF($AK26,1,0),
+IF($AL26,1,0),
+IF($AM26,1,0),
+IF($AN26,1,0))</f>
+        <v/>
+      </c>
+      <c r="L26" s="3">
+        <f>IF($E26, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P26, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W26, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R26, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q26, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S26, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F26, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O26, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M26" s="3">
+        <f>IF(NOT($H26 = $C26),
+  $B26 &amp; " " &amp; IF($H26, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C26, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y26, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W26" s="3">
+        <f>$X26 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="3">
+        <f>AND($U26, $V26)</f>
+        <v/>
+      </c>
+      <c r="Z26" s="2" t="inlineStr"/>
+      <c r="AA26" s="3">
+        <f>IF($X26 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM26" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO26" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP26" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>songbird-song-learned-dialects</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Songbird Song (learned dialects)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="3">
+        <f>$E27 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3">
+        <f>"Is " &amp; $B27 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H27" s="3">
+        <f>OR(
+  AND(
+    $E27,
+    $P27,
+    $W27,
+    $R27,
+    $Q27,
+    $S27,
+    NOT($F27),
+    NOT($O27)
+  ),
+  $K27 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I27" s="3">
+        <f>AND(
+  $AO27,
+  $AD27,
+  $AE27,
+  $AF27,
+  $AG27,
+  $AH27,
+  $AI27,
+  $AJ27
+)</f>
+        <v/>
+      </c>
+      <c r="J27" s="3">
+        <f>AND(
+  $I27,
+  $AK27,
+  $AL27
+)</f>
+        <v/>
+      </c>
+      <c r="K27" s="3">
+        <f>SUM(IF($AD27,1,0),
+IF($AE27,1,0),
+IF($AF27,1,0),
+IF($AG27,1,0),
+IF($AH27,1,0),
+IF($AI27,1,0),
+IF($AJ27,1,0),
+IF($AK27,1,0),
+IF($AL27,1,0),
+IF($AM27,1,0),
+IF($AN27,1,0))</f>
+        <v/>
+      </c>
+      <c r="L27" s="3">
+        <f>IF($E27, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P27, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W27, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R27, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q27, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S27, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F27, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O27, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M27" s="3">
+        <f>IF(NOT($H27 = $C27),
+  $B27 &amp; " " &amp; IF($H27, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C27, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y27, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W27" s="3">
+        <f>$X27 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="3">
+        <f>AND($U27, $V27)</f>
+        <v/>
+      </c>
+      <c r="Z27" s="2" t="inlineStr"/>
+      <c r="AA27" s="3">
+        <f>IF($X27 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM27" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO27" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP27" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>killer-whale-pod-dialects</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Killer Whale Pod Dialects</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="3">
+        <f>$E28 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3">
+        <f>"Is " &amp; $B28 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H28" s="3">
+        <f>OR(
+  AND(
+    $E28,
+    $P28,
+    $W28,
+    $R28,
+    $Q28,
+    $S28,
+    NOT($F28),
+    NOT($O28)
+  ),
+  $K28 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I28" s="3">
+        <f>AND(
+  $AO28,
+  $AD28,
+  $AE28,
+  $AF28,
+  $AG28,
+  $AH28,
+  $AI28,
+  $AJ28
+)</f>
+        <v/>
+      </c>
+      <c r="J28" s="3">
+        <f>AND(
+  $I28,
+  $AK28,
+  $AL28
+)</f>
+        <v/>
+      </c>
+      <c r="K28" s="3">
+        <f>SUM(IF($AD28,1,0),
+IF($AE28,1,0),
+IF($AF28,1,0),
+IF($AG28,1,0),
+IF($AH28,1,0),
+IF($AI28,1,0),
+IF($AJ28,1,0),
+IF($AK28,1,0),
+IF($AL28,1,0),
+IF($AM28,1,0),
+IF($AN28,1,0))</f>
+        <v/>
+      </c>
+      <c r="L28" s="3">
+        <f>IF($E28, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P28, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W28, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R28, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q28, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S28, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F28, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O28, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M28" s="3">
+        <f>IF(NOT($H28 = $C28),
+  $B28 &amp; " " &amp; IF($H28, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C28, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y28, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W28" s="3">
+        <f>$X28 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <f>AND($U28, $V28)</f>
+        <v/>
+      </c>
+      <c r="Z28" s="2" t="inlineStr"/>
+      <c r="AA28" s="3">
+        <f>IF($X28 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN28" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO28" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>dolphin-signature-whistles</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Dolphin Signature Whistles</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="3">
+        <f>$E29 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <f>"Is " &amp; $B29 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H29" s="3">
+        <f>OR(
+  AND(
+    $E29,
+    $P29,
+    $W29,
+    $R29,
+    $Q29,
+    $S29,
+    NOT($F29),
+    NOT($O29)
+  ),
+  $K29 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I29" s="3">
+        <f>AND(
+  $AO29,
+  $AD29,
+  $AE29,
+  $AF29,
+  $AG29,
+  $AH29,
+  $AI29,
+  $AJ29
+)</f>
+        <v/>
+      </c>
+      <c r="J29" s="3">
+        <f>AND(
+  $I29,
+  $AK29,
+  $AL29
+)</f>
+        <v/>
+      </c>
+      <c r="K29" s="3">
+        <f>SUM(IF($AD29,1,0),
+IF($AE29,1,0),
+IF($AF29,1,0),
+IF($AG29,1,0),
+IF($AH29,1,0),
+IF($AI29,1,0),
+IF($AJ29,1,0),
+IF($AK29,1,0),
+IF($AL29,1,0),
+IF($AM29,1,0),
+IF($AN29,1,0))</f>
+        <v/>
+      </c>
+      <c r="L29" s="3">
+        <f>IF($E29, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P29, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W29, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R29, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q29, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S29, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F29, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O29, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M29" s="3">
+        <f>IF(NOT($H29 = $C29),
+  $B29 &amp; " " &amp; IF($H29, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C29, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y29, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <f>$X29 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <f>AND($U29, $V29)</f>
+        <v/>
+      </c>
+      <c r="Z29" s="2" t="inlineStr"/>
+      <c r="AA29" s="3">
+        <f>IF($X29 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO29" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP29" s="2" t="inlineStr">
+        <is>
+          <t>VocalAuditory</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ant-pheromone-trail-system</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Ant Pheromone Trail System</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="3">
+        <f>$E30 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" s="3">
+        <f>"Is " &amp; $B30 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H30" s="3">
+        <f>OR(
+  AND(
+    $E30,
+    $P30,
+    $W30,
+    $R30,
+    $Q30,
+    $S30,
+    NOT($F30),
+    NOT($O30)
+  ),
+  $K30 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I30" s="3">
+        <f>AND(
+  $AO30,
+  $AD30,
+  $AE30,
+  $AF30,
+  $AG30,
+  $AH30,
+  $AI30,
+  $AJ30
+)</f>
+        <v/>
+      </c>
+      <c r="J30" s="3">
+        <f>AND(
+  $I30,
+  $AK30,
+  $AL30
+)</f>
+        <v/>
+      </c>
+      <c r="K30" s="3">
+        <f>SUM(IF($AD30,1,0),
+IF($AE30,1,0),
+IF($AF30,1,0),
+IF($AG30,1,0),
+IF($AH30,1,0),
+IF($AI30,1,0),
+IF($AJ30,1,0),
+IF($AK30,1,0),
+IF($AL30,1,0),
+IF($AM30,1,0),
+IF($AN30,1,0))</f>
+        <v/>
+      </c>
+      <c r="L30" s="3">
+        <f>IF($E30, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P30, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W30, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R30, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q30, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S30, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F30, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O30, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M30" s="3">
+        <f>IF(NOT($H30 = $C30),
+  $B30 &amp; " " &amp; IF($H30, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C30, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y30, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <f>$X30 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <f>AND($U30, $V30)</f>
+        <v/>
+      </c>
+      <c r="Z30" s="2" t="inlineStr"/>
+      <c r="AA30" s="3">
+        <f>IF($X30 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL30" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO30" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP30" s="2" t="inlineStr">
+        <is>
+          <t>Tactile</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>cuttlefish-chromatophore-displays</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Cuttlefish Chromatophore Displays</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="3">
+        <f>$E31 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3">
+        <f>"Is " &amp; $B31 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H31" s="3">
+        <f>OR(
+  AND(
+    $E31,
+    $P31,
+    $W31,
+    $R31,
+    $Q31,
+    $S31,
+    NOT($F31),
+    NOT($O31)
+  ),
+  $K31 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I31" s="3">
+        <f>AND(
+  $AO31,
+  $AD31,
+  $AE31,
+  $AF31,
+  $AG31,
+  $AH31,
+  $AI31,
+  $AJ31
+)</f>
+        <v/>
+      </c>
+      <c r="J31" s="3">
+        <f>AND(
+  $I31,
+  $AK31,
+  $AL31
+)</f>
+        <v/>
+      </c>
+      <c r="K31" s="3">
+        <f>SUM(IF($AD31,1,0),
+IF($AE31,1,0),
+IF($AF31,1,0),
+IF($AG31,1,0),
+IF($AH31,1,0),
+IF($AI31,1,0),
+IF($AJ31,1,0),
+IF($AK31,1,0),
+IF($AL31,1,0),
+IF($AM31,1,0),
+IF($AN31,1,0))</f>
+        <v/>
+      </c>
+      <c r="L31" s="3">
+        <f>IF($E31, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P31, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W31, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R31, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q31, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S31, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F31, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O31, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M31" s="3">
+        <f>IF(NOT($H31 = $C31),
+  $B31 &amp; " " &amp; IF($H31, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C31, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y31, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W31" s="3">
+        <f>$X31 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <f>AND($U31, $V31)</f>
+        <v/>
+      </c>
+      <c r="Z31" s="2" t="inlineStr"/>
+      <c r="AA31" s="3">
+        <f>IF($X31 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM31" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO31" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP31" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>nicaraguan-sign-language-early-cohort</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Nicaraguan Sign Language (early cohort)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="3">
+        <f>$E32 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <f>"Is " &amp; $B32 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H32" s="3">
+        <f>OR(
+  AND(
+    $E32,
+    $P32,
+    $W32,
+    $R32,
+    $Q32,
+    $S32,
+    NOT($F32),
+    NOT($O32)
+  ),
+  $K32 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I32" s="3">
+        <f>AND(
+  $AO32,
+  $AD32,
+  $AE32,
+  $AF32,
+  $AG32,
+  $AH32,
+  $AI32,
+  $AJ32
+)</f>
+        <v/>
+      </c>
+      <c r="J32" s="3">
+        <f>AND(
+  $I32,
+  $AK32,
+  $AL32
+)</f>
+        <v/>
+      </c>
+      <c r="K32" s="3">
+        <f>SUM(IF($AD32,1,0),
+IF($AE32,1,0),
+IF($AF32,1,0),
+IF($AG32,1,0),
+IF($AH32,1,0),
+IF($AI32,1,0),
+IF($AJ32,1,0),
+IF($AK32,1,0),
+IF($AL32,1,0),
+IF($AM32,1,0),
+IF($AN32,1,0))</f>
+        <v/>
+      </c>
+      <c r="L32" s="3">
+        <f>IF($E32, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P32, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W32, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R32, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q32, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S32, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F32, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O32, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M32" s="3">
+        <f>IF(NOT($H32 = $C32),
+  $B32 &amp; " " &amp; IF($H32, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C32, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y32, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V32" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
+        <f>$X32 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="3">
+        <f>AND($U32, $V32)</f>
+        <v/>
+      </c>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="3">
+        <f>IF($X32 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AJ32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AK32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AL32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AM32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AN32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO32" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>VisualGestural</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>homesign-single-child</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Homesign (single child)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="3">
+        <f>$E33 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" s="3">
+        <f>"Is " &amp; $B33 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H33" s="3">
+        <f>OR(
+  AND(
+    $E33,
+    $P33,
+    $W33,
+    $R33,
+    $Q33,
+    $S33,
+    NOT($F33),
+    NOT($O33)
+  ),
+  $K33 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I33" s="3">
+        <f>AND(
+  $AO33,
+  $AD33,
+  $AE33,
+  $AF33,
+  $AG33,
+  $AH33,
+  $AI33,
+  $AJ33
+)</f>
+        <v/>
+      </c>
+      <c r="J33" s="3">
+        <f>AND(
+  $I33,
+  $AK33,
+  $AL33
+)</f>
+        <v/>
+      </c>
+      <c r="K33" s="3">
+        <f>SUM(IF($AD33,1,0),
+IF($AE33,1,0),
+IF($AF33,1,0),
+IF($AG33,1,0),
+IF($AH33,1,0),
+IF($AI33,1,0),
+IF($AJ33,1,0),
+IF($AK33,1,0),
+IF($AL33,1,0),
+IF($AM33,1,0),
+IF($AN33,1,0))</f>
+        <v/>
+      </c>
+      <c r="L33" s="3">
+        <f>IF($E33, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P33, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W33, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R33, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q33, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S33, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F33, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O33, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M33" s="3">
+        <f>IF(NOT($H33 = $C33),
+  $B33 &amp; " " &amp; IF($H33, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C33, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y33, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W33" s="3">
+        <f>$X33 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="3">
+        <f>AND($U33, $V33)</f>
+        <v/>
+      </c>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="3">
+        <f>IF($X33 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN33" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO33" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>bonobo-lexigram-keyboard-communication</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Bonobo/Lexigram Keyboard Communication</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="3">
+        <f>$E34 = TRUE()</f>
+        <v/>
+      </c>
+      <c r="E34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="F34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" s="3">
+        <f>"Is " &amp; $B34 &amp; " a language?"</f>
+        <v/>
+      </c>
+      <c r="H34" s="3">
+        <f>OR(
+  AND(
+    $E34,
+    $P34,
+    $W34,
+    $R34,
+    $Q34,
+    $S34,
+    NOT($F34),
+    NOT($O34)
+  ),
+  $K34 &gt; 0
+)</f>
+        <v/>
+      </c>
+      <c r="I34" s="3">
+        <f>AND(
+  $AO34,
+  $AD34,
+  $AE34,
+  $AF34,
+  $AG34,
+  $AH34,
+  $AI34,
+  $AJ34
+)</f>
+        <v/>
+      </c>
+      <c r="J34" s="3">
+        <f>AND(
+  $I34,
+  $AK34,
+  $AL34
+)</f>
+        <v/>
+      </c>
+      <c r="K34" s="3">
+        <f>SUM(IF($AD34,1,0),
+IF($AE34,1,0),
+IF($AF34,1,0),
+IF($AG34,1,0),
+IF($AH34,1,0),
+IF($AI34,1,0),
+IF($AJ34,1,0),
+IF($AK34,1,0),
+IF($AL34,1,0),
+IF($AM34,1,0),
+IF($AN34,1,0))</f>
+        <v/>
+      </c>
+      <c r="L34" s="3">
+        <f>IF($E34, "Has Syntax", "No Syntax") &amp; " &amp; " &amp; IF($P34, "Requires Parsing", "No Parsing Neede") &amp; " &amp; " &amp; IF($W34, "Describes the thing", "Is the Thing") &amp; " &amp; " &amp; IF($R34, "Has Linear Decoding Pressure", "No Decoding Pressure") &amp; " &amp; " &amp; IF($Q34, "Resolves to AST", "No AST") &amp; ", " &amp; IF($S34, "Is Stable Ontology", "Not 'Ontology'") &amp; " AND " &amp; IF($F34, "Can Be Held", "Can't Be Held") &amp; ", " &amp;IF($O34, "Has Identity", "Has no Identity")</f>
+        <v/>
+      </c>
+      <c r="M34" s="3">
+        <f>IF(NOT($H34 = $C34),
+  $B34 &amp; " " &amp; IF($H34, "Is", "Isn't") &amp; " a Family Feud Language, but " &amp; 
+  IF($C34, "Is", "Is Not") &amp; " marked as a 'Language Candidate.'", "") &amp; IF($Y34, " - Open World vs. Closed World Conflict.", "")</f>
+        <v/>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>Natural Language</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="P34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="R34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="S34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="U34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="V34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="W34" s="3">
+        <f>$X34 &gt; 1</f>
+        <v/>
+      </c>
+      <c r="X34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <f>AND($U34, $V34)</f>
+        <v/>
+      </c>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="3">
+        <f>IF($X34 = 1, "IsMirrorOf", "IsDescriptionOf")</f>
+        <v/>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH34" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AI34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AL34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AN34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP34" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4137,7 +7758,39 @@
 BEGIN
   RETURN ('Is ' || (SELECT NULLIF(name, '''') FROM language_candidates WHERE language_candidate_id = p_language_candidate_id) || ' a language?')::text;
 END;
-$function$
+$function$;
+CREATE OR REPLACE FUNCTION public.calc_language_candidates_bio_hockett_score(p_language_candidate_id text)
+ RETURNS integer
+ LANGUAGE plpgsql
+ STABLE SECURITY DEFINER
+AS $function$
+DECLARE
+    candidate_record RECORD;
+BEGIN
+    -- Select the required attributes for the given language candidate ID
+    SELECT bio_has_semanticity, bio_has_arbitrariness, bio_has_discreteness, 
+           bio_has_duality_of_patterning, bio_has_productivity, 
+           bio_has_displacement, bio_has_cultural_transmission, 
+           bio_has_interchangeability, bio_has_feedback, 
+           bio_has_broadcast_transmission, bio_has_rapid_fading
+    INTO candidate_record
+    FROM language_candidates
+    WHERE language_candidate_id = p_language_candidate_id;
+    -- Calculate and return the Hockett score by summing up the boolean attributes
+    RETURN 
+        COALESCE(candidate_record.bio_has_semanticity, FALSE)::int +
+        COALESCE(candidate_record.bio_has_arbitrariness, FALSE)::int +
+        COALESCE(candidate_record.bio_has_discreteness, FALSE)::int +
+        COALESCE(candidate_record.bio_has_duality_of_patterning, FALSE)::int +
+        COALESCE(candidate_record.bio_has_productivity, FALSE)::int +
+        COALESCE(candidate_record.bio_has_displacement, FALSE)::int +
+        COALESCE(candidate_record.bio_has_cultural_transmission, FALSE)::int +
+        COALESCE(candidate_record.bio_has_interchangeability, FALSE)::int +
+        COALESCE(candidate_record.bio_has_feedback, FALSE)::int +
+        COALESCE(candidate_record.bio_has_broadcast_transmission, FALSE)::int +
+        COALESCE(candidate_record.bio_has_rapid_fading, FALSE)::int;
+END;
+$function$;
 </t>
         </is>
       </c>
